--- a/tools/1000_websites_sorter/domain_data.xlsx
+++ b/tools/1000_websites_sorter/domain_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shake\Documents\GitHub\PQBench\tools\1000_websites_sorter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF95339-8E4C-4BDF-B14D-779393CCE8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5B8DB6-C922-4796-AF82-946CFB4A5A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -236,9 +236,6 @@
     <t>https://www.aloyoga.com/en-il/pages/alo-events</t>
   </si>
   <si>
-    <t>https://www.alibaba.com/product-detail/Portable-Mini-Ultra-thin-Rechargeable-Wireless_1601390200997.html?spm=a2700.details.buy_together.2.3fc6593eYFnuPo</t>
-  </si>
-  <si>
     <t>https://www.snapchat.com/</t>
   </si>
   <si>
@@ -2832,12 +2829,15 @@
   <si>
     <t>btnPrimary</t>
   </si>
+  <si>
+    <t>צריך ללחוץ X על הפרסומת</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2952,8 +2952,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2995,6 +3002,11 @@
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -3033,7 +3045,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
@@ -3041,8 +3053,9 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3095,8 +3108,16 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="7" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="7" applyBorder="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
+    <cellStyle name="Bad" xfId="7" builtinId="27"/>
     <cellStyle name="Excel Built-in Bad" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Excel Built-in Bad 1" xfId="5" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Excel Built-in Good" xfId="4" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
@@ -3382,7 +3403,7 @@
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="38" t="s">
         <v>2</v>
       </c>
     </row>
@@ -3424,7 +3445,10 @@
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
+      <c r="A9" t="s">
+        <v>919</v>
+      </c>
+      <c r="B9" s="39" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3456,7 +3480,7 @@
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="39" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3503,7 +3527,7 @@
       <c r="A22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="39" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3615,7 +3639,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="40" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3630,7 +3654,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="39" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3646,7 +3670,7 @@
       <c r="A46" t="s">
         <v>58</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="39" t="s">
         <v>59</v>
       </c>
     </row>
@@ -3731,20 +3755,20 @@
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
       <c r="B63" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>77</v>
-      </c>
       <c r="B64" s="3" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3754,110 +3778,110 @@
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>81</v>
+      </c>
       <c r="B67" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>84</v>
-      </c>
       <c r="B69" s="8" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>86</v>
+      </c>
       <c r="B70" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>87</v>
-      </c>
+      <c r="A71" s="4"/>
       <c r="B71" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
       <c r="B72" s="8" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="4" t="s">
+        <v>90</v>
+      </c>
       <c r="B73" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="4" t="s">
-        <v>95</v>
+      <c r="A76" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="B78" s="8" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="B79" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>101</v>
-      </c>
       <c r="B80" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" s="4"/>
       <c r="B81" s="8" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
       <c r="B82" s="8" t="s">
         <v>104</v>
       </c>
@@ -3873,22 +3897,22 @@
       </c>
     </row>
     <row r="85" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="B85" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="B87" s="8" t="s">
         <v>110</v>
       </c>
@@ -3913,11 +3937,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B92" s="8" t="s">
-        <v>115</v>
-      </c>
-    </row>
+    <row r="92" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
     <row r="95" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B95" s="9"/>
     </row>
@@ -4007,36 +4027,35 @@
     <hyperlink ref="B41" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
     <hyperlink ref="B45" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
     <hyperlink ref="B46" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="B48" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="B49" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="B50" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="B51" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="B52" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="B53" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="B55" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="B56" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="B57" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="B58" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="B59" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="B60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="B61" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="B62" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="B63" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="B64" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="B65" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="B66" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="B67" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
-    <hyperlink ref="B68" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
-    <hyperlink ref="B69" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
-    <hyperlink ref="B70" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
-    <hyperlink ref="B71" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
-    <hyperlink ref="B72" r:id="rId48" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
-    <hyperlink ref="B73" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
-    <hyperlink ref="B76" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
-    <hyperlink ref="B79" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
-    <hyperlink ref="B80" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
-    <hyperlink ref="B83" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
-    <hyperlink ref="B86" r:id="rId54" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
+    <hyperlink ref="B48" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B49" r:id="rId26" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="B50" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B51" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="B52" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="B54" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="B55" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="B56" r:id="rId32" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="B57" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="B58" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="B59" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="B60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="B61" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="B62" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="B63" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="B64" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="B65" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="B66" r:id="rId42" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="B67" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
+    <hyperlink ref="B68" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002C000000}"/>
+    <hyperlink ref="B69" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
+    <hyperlink ref="B70" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
+    <hyperlink ref="B71" r:id="rId47" xr:uid="{00000000-0004-0000-0000-00002F000000}"/>
+    <hyperlink ref="B72" r:id="rId48" xr:uid="{00000000-0004-0000-0000-000030000000}"/>
+    <hyperlink ref="B75" r:id="rId49" xr:uid="{00000000-0004-0000-0000-000031000000}"/>
+    <hyperlink ref="B78" r:id="rId50" xr:uid="{00000000-0004-0000-0000-000032000000}"/>
+    <hyperlink ref="B79" r:id="rId51" xr:uid="{00000000-0004-0000-0000-000033000000}"/>
+    <hyperlink ref="B82" r:id="rId52" xr:uid="{00000000-0004-0000-0000-000034000000}"/>
+    <hyperlink ref="B85" r:id="rId53" xr:uid="{00000000-0004-0000-0000-000035000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4065,22 +4084,22 @@
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -4088,20 +4107,20 @@
         <v>39</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -4111,446 +4130,446 @@
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>127</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>129</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>134</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>140</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>145</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>147</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>150</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>154</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="8" t="s">
         <v>156</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" s="8" t="s">
         <v>158</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B32" s="8" t="s">
         <v>161</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="8" t="s">
         <v>163</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" s="8" t="s">
         <v>165</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
       <c r="B37" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B38" s="8" t="s">
         <v>172</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4"/>
       <c r="B40" s="8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>176</v>
+      </c>
+      <c r="B41" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B43" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="8" t="s">
         <v>183</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>184</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
       <c r="B46" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="8" t="s">
         <v>188</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>190</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B50" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>195</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B52" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B53" s="8" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
       <c r="B54" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B55" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
       <c r="B56" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B57" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B58" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" s="8" t="s">
         <v>211</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B66" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
+        <v>218</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -4558,69 +4577,69 @@
         <v>36</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B71" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B72" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>229</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>230</v>
+      </c>
+      <c r="B75" s="8" t="s">
         <v>231</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B78" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -4768,502 +4787,502 @@
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="12" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="12" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B15" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B27" s="12" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="12" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B38" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B39" s="12" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" s="12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B41" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B43" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B44" s="12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B46" s="12" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B47" s="12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B48" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B49" s="12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="51" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B51" s="12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B52" s="12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="53" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B53" s="12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B54" s="12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B55" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B56" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B57" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="58" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B58" s="12" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B59" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B60" s="12" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B61" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B62" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="63" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B63" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="64" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B64" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B66" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B67" s="12" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B68" s="12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B69" s="12" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B70" s="12" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B71" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="72" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B72" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="73" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B73" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="74" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B74" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B75" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="76" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B76" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="77" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B77" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="78" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B78" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B79" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="80" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B80" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B81" s="12" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="82" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B82" s="12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B83" s="12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="84" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B84" s="12" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B85" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B86" s="12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B87" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B88" s="12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B89" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="90" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B90" s="12" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B91" s="12" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="92" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B92" s="12" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B93" s="12" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B94" s="12" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B95" s="12" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B96" s="12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="97" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B97" s="12" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="98" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B98" s="12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="99" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B99" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="100" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B100" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="101" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B101" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="111" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -5706,582 +5725,582 @@
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="14" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
       <c r="B5" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="14" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="14" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="14" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="14" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="14" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="14" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D20" s="15"/>
     </row>
     <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D21" s="16"/>
     </row>
     <row r="22" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
       <c r="B22" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D22" s="15"/>
     </row>
     <row r="23" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D23" s="16"/>
     </row>
     <row r="24" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D24" s="15"/>
     </row>
     <row r="25" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="14" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D25" s="16"/>
     </row>
     <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D26" s="17"/>
     </row>
     <row r="27" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D27" s="17"/>
     </row>
     <row r="28" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D28" s="18"/>
     </row>
     <row r="29" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D29" s="18"/>
     </row>
     <row r="30" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="14" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D30" s="18"/>
     </row>
     <row r="31" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="14" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D31" s="18"/>
     </row>
     <row r="32" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="14" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D32" s="18"/>
     </row>
     <row r="33" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="14" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D33" s="18"/>
     </row>
     <row r="34" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="14" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D34" s="18"/>
     </row>
     <row r="35" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="14" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D35" s="18"/>
     </row>
     <row r="36" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="14" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D36" s="18"/>
     </row>
     <row r="37" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
       <c r="B37" s="14" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="5"/>
       <c r="B38" s="14" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5"/>
       <c r="B39" s="14" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="14" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="14" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="19"/>
       <c r="B45" s="14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="5"/>
       <c r="B46" s="14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="5"/>
       <c r="B49" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="5"/>
       <c r="B51" s="14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5"/>
       <c r="B52" s="14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5"/>
       <c r="B54" s="14" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5"/>
       <c r="B56" s="14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="5"/>
       <c r="B57" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="5"/>
       <c r="B58" s="14" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="14" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="5"/>
       <c r="B60" s="14" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="5"/>
       <c r="B61" s="14" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="5"/>
       <c r="B62" s="14" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="5"/>
       <c r="B63" s="14" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="5"/>
       <c r="B64" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="5"/>
       <c r="B65" s="14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="5"/>
       <c r="B66" s="14" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="5"/>
       <c r="B67" s="14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="5"/>
       <c r="B68" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="5"/>
       <c r="B69" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="14" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="5"/>
       <c r="B73" s="14" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="5"/>
       <c r="B74" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="5"/>
       <c r="B77" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="5"/>
       <c r="B78" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="5"/>
       <c r="B79" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="5"/>
       <c r="B80" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="5"/>
       <c r="B81" s="14" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="5"/>
       <c r="B82" s="14" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="5"/>
       <c r="B83" s="14" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="5"/>
       <c r="B84" s="14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="5"/>
       <c r="B85" s="14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="5"/>
       <c r="B86" s="14" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="5"/>
       <c r="B87" s="14" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B88" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="5"/>
       <c r="B89" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="5"/>
       <c r="B90" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="5"/>
       <c r="B91" s="14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="5"/>
       <c r="B92" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="5"/>
       <c r="B93" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="5"/>
       <c r="B94" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B95" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="5"/>
       <c r="B96" s="14" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -6439,612 +6458,612 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B2" s="26" t="s">
         <v>434</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>436</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="26" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B5" s="26" t="s">
         <v>439</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="28"/>
     </row>
     <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>442</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>443</v>
       </c>
       <c r="E7" s="27"/>
     </row>
     <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B8" s="26" t="s">
         <v>444</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>445</v>
       </c>
       <c r="F8" s="29"/>
     </row>
     <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B9" s="26" t="s">
         <v>446</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B10" s="26" t="s">
         <v>448</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>449</v>
       </c>
       <c r="G10" s="27"/>
     </row>
     <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="B11" s="26" t="s">
         <v>450</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="B12" s="26" t="s">
         <v>452</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="B13" s="26" t="s">
         <v>454</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" s="26" t="s">
         <v>456</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B15" s="26" t="s">
         <v>458</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B16" s="26" t="s">
         <v>460</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="26" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="B18" s="26" t="s">
         <v>463</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B21" s="26" t="s">
         <v>467</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>469</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" s="26" t="s">
         <v>471</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="5"/>
       <c r="B24" s="8" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="B25" s="26" t="s">
         <v>474</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="30"/>
       <c r="B26" s="26" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="8" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="5"/>
       <c r="B28" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
+        <v>478</v>
+      </c>
+      <c r="B29" s="26" t="s">
         <v>479</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
+        <v>481</v>
+      </c>
+      <c r="B31" s="26" t="s">
         <v>482</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="8" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="30" t="s">
+        <v>484</v>
+      </c>
+      <c r="B33" s="26" t="s">
         <v>485</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="30" t="s">
+        <v>486</v>
+      </c>
+      <c r="B34" s="26" t="s">
         <v>487</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="30" t="s">
+        <v>488</v>
+      </c>
+      <c r="B35" s="26" t="s">
         <v>489</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="B36" s="26" t="s">
         <v>491</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="30" t="s">
+        <v>492</v>
+      </c>
+      <c r="B37" s="26" t="s">
         <v>493</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B38" s="26" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
+        <v>495</v>
+      </c>
+      <c r="B39" s="26" t="s">
         <v>496</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="B40" s="26" t="s">
         <v>498</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="30" t="s">
+        <v>500</v>
+      </c>
+      <c r="B42" s="26" t="s">
         <v>501</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="30" t="s">
+        <v>502</v>
+      </c>
+      <c r="B43" s="26" t="s">
         <v>503</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="B44" s="26" t="s">
         <v>505</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="B45" s="26" t="s">
         <v>507</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B46" s="26" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="5"/>
       <c r="B47" s="8" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="30" t="s">
+        <v>510</v>
+      </c>
+      <c r="B48" s="26" t="s">
         <v>511</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="B49" s="26" t="s">
         <v>513</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="30"/>
       <c r="B50" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="30" t="s">
+        <v>515</v>
+      </c>
+      <c r="B51" s="26" t="s">
         <v>516</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="30" t="s">
+        <v>517</v>
+      </c>
+      <c r="B52" s="26" t="s">
         <v>518</v>
-      </c>
-      <c r="B52" s="26" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B53" s="26" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B55" s="26" t="s">
         <v>522</v>
-      </c>
-      <c r="B55" s="26" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="B56" s="26" t="s">
         <v>524</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="B58" s="26" t="s">
         <v>527</v>
-      </c>
-      <c r="B58" s="26" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="B60" s="26" t="s">
         <v>530</v>
-      </c>
-      <c r="B60" s="26" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="B61" s="26" t="s">
         <v>532</v>
-      </c>
-      <c r="B61" s="26" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B62" s="26" t="s">
         <v>534</v>
-      </c>
-      <c r="B62" s="26" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="B63" s="26" t="s">
         <v>536</v>
-      </c>
-      <c r="B63" s="26" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>538</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>541</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>543</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="B68" s="8" t="s">
         <v>545</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B69" s="26" t="s">
         <v>547</v>
-      </c>
-      <c r="B69" s="26" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="B70" s="26" t="s">
         <v>549</v>
-      </c>
-      <c r="B70" s="26" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B71" s="26" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="26" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B73" s="8" t="s">
         <v>553</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B74" s="8" t="s">
         <v>555</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
       <c r="B75" s="8" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B76" s="8" t="s">
         <v>558</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B77" s="8" t="s">
         <v>560</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B78" s="8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B79" s="8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>563</v>
+      </c>
+      <c r="B80" s="8" t="s">
         <v>564</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B81" s="8" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="B82" s="8" t="s">
         <v>567</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B83" s="8" t="s">
         <v>569</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -7131,599 +7150,599 @@
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B2" s="34" t="s">
         <v>571</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="34" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B4" s="34" t="s">
         <v>574</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>575</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>576</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B6" s="34" t="s">
         <v>578</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>579</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>580</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>582</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="34" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>584</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>585</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>587</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>588</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="34" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>591</v>
+      </c>
+      <c r="B15" s="34" t="s">
         <v>592</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>593</v>
+      </c>
+      <c r="B16" s="34" t="s">
         <v>594</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>595</v>
+      </c>
+      <c r="B17" s="34" t="s">
         <v>596</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="12" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="12" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="34" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="12" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" s="12" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="34" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="34" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="12" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B27" s="12" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B28" s="12" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B30" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="12" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="12" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B33" s="12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="34" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="12" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" s="34" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B36" s="12" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" s="12" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B38" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B39" s="12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B40" s="12" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B41" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="42" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B42" s="12" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="43" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B43" s="34" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B44" s="34" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="34" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B46" s="12" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B47" s="12" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="48" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B48" s="12" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B49" s="12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="12" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="51" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B51" s="34" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B52" s="12" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="53" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B53" s="12" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B54" s="34" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B55" s="34" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B56" s="34" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="57" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B57" s="34" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="58" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B58" s="34" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="59" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B59" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="60" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B60" s="12" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="61" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B61" s="34" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B62" s="12" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="63" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B63" s="34" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="64" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B64" s="34" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="65" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="34" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B66" s="12" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B67" s="12" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="68" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B68" s="34" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="69" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B69" s="12" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B70" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="71" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B71" s="34" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="72" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B72" s="12" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="73" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B73" s="34" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="74" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B74" s="34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="75" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B75" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="76" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B76" s="34" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="77" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B77" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="78" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B78" s="12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="79" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B79" s="34" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="80" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B80" s="12" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="81" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B81" s="12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="82" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B82" s="34" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="83" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B83" s="34" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="84" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B84" s="12" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="85" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B85" s="12" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="86" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B86" s="12" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="87" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B87" s="12" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="88" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B88" s="12" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="89" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B89" s="12" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="90" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B90" s="12" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="91" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B91" s="12" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="92" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B92" s="34" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="93" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B93" s="12" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="94" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B94" s="34" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="95" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B95" s="12" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="96" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B96" s="12" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B97" s="34" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B98" s="12" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B99" s="12" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>679</v>
+      </c>
+      <c r="B100" s="35" t="s">
         <v>680</v>
-      </c>
-      <c r="B100" s="35" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B101" s="35" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B102" s="35" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
+        <v>683</v>
+      </c>
+      <c r="B103" s="35" t="s">
         <v>684</v>
-      </c>
-      <c r="B103" s="35" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B104" s="35" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B105" s="35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B106" s="35" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B107" s="35" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B108" s="35" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
+        <v>690</v>
+      </c>
+      <c r="B109" s="35" t="s">
         <v>691</v>
-      </c>
-      <c r="B109" s="35" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
@@ -7781,213 +7800,213 @@
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
+        <v>692</v>
+      </c>
+      <c r="B2" s="12" t="s">
         <v>693</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="30"/>
       <c r="B3" s="36" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="36" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B5" s="36" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="36" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="36" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="36" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>700</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>701</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="36" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="36" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="36" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="36" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="36" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="30" t="s">
+        <v>707</v>
+      </c>
+      <c r="B15" s="36" t="s">
         <v>708</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="36" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>712</v>
+      </c>
+      <c r="B19" s="36" t="s">
         <v>713</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="B20" s="36" t="s">
         <v>715</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="B21" s="36" t="s">
         <v>717</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
+        <v>718</v>
+      </c>
+      <c r="B22" s="36" t="s">
         <v>719</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="5"/>
       <c r="B23" s="36" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="36" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="36" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="5"/>
       <c r="B27" s="36" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="30"/>
       <c r="B29" s="36" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="36" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="36" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="5"/>
       <c r="B32" s="36" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="30"/>
       <c r="B33" s="36" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="36" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="36" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="36" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -7995,230 +8014,230 @@
         <v>36</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="B38" s="36" t="s">
         <v>736</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="B39" s="36" t="s">
         <v>738</v>
-      </c>
-      <c r="B39" s="36" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="5"/>
       <c r="B40" s="36" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="5"/>
       <c r="B41" s="36" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="5"/>
       <c r="B42" s="36" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="36" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="5"/>
       <c r="B44" s="36" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="36" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="30"/>
       <c r="B46" s="36" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B47" s="36" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="5"/>
       <c r="B48" s="36" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B49" s="36" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5"/>
       <c r="B53" s="36" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="30"/>
       <c r="B54" s="36" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="5"/>
       <c r="B55" s="36" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
+        <v>755</v>
+      </c>
+      <c r="B56" s="36" t="s">
         <v>756</v>
-      </c>
-      <c r="B56" s="36" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B57" s="36" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B58" s="36" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="5"/>
       <c r="B59" s="36" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
+        <v>760</v>
+      </c>
+      <c r="B60" s="36" t="s">
         <v>761</v>
-      </c>
-      <c r="B60" s="36" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B61" s="36" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B62" s="36" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B63" s="36" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B64" s="36" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="36" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B66" s="36" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B67" s="36" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B68" s="36" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B69" s="36" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="5"/>
       <c r="B70" s="36" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="5"/>
       <c r="B71" s="36" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="5"/>
       <c r="B72" s="36" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B73" s="36" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B74" s="36" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="5"/>
       <c r="B75" s="36" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="5"/>
       <c r="B76" s="36" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -8226,81 +8245,81 @@
         <v>39</v>
       </c>
       <c r="B77" s="36" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
       <c r="B78" s="36" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
       <c r="B80" s="36" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="36" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="36" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="36" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
       <c r="B84" s="36" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="36" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="36" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="36" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
       <c r="B88" s="36" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="36" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="14.4" x14ac:dyDescent="0.3"/>
@@ -8401,203 +8420,203 @@
         <v>39</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B3" s="36" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B4" s="36" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>795</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B6" s="36" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="36" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B8" s="36" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B9" s="36" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B10" s="36" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B11" s="36" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="B12" s="36" t="s">
         <v>803</v>
-      </c>
-      <c r="B12" s="36" t="s">
-        <v>804</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B13" s="36" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B14" s="36" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="36" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B16" s="36" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B17" s="36" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B19" s="36" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B20" s="36" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B23" s="36" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B24" s="36" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B25" s="36" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B26" s="36" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B27" s="36" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B28" s="36" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B29" s="36" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="36" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B31" s="36" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B32" s="36" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B33" s="36" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B34" s="36" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B35" s="36" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B36" s="36" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B37" s="36" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="B38" s="36" t="s">
         <v>830</v>
-      </c>
-      <c r="B38" s="36" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B39" s="36" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -8605,53 +8624,53 @@
         <v>39</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="B41" s="36" t="s">
         <v>834</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B42" s="36" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B43" s="36" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B44" s="36" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B45" s="36" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
+        <v>839</v>
+      </c>
+      <c r="B46" s="36" t="s">
         <v>840</v>
-      </c>
-      <c r="B46" s="36" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B47" s="36" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B48" s="36" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
@@ -8659,373 +8678,373 @@
         <v>39</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B50" s="36" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B51" s="36" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B52" s="36" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="36" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B54" s="36" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B55" s="36" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B56" s="36" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B57" s="36" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B58" s="36" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B59" s="36" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B60" s="36" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B61" s="36" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B62" s="36" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B63" s="36" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B64" s="36" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B65" s="36" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B66" s="36" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B67" s="36" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B68" s="36" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B69" s="36" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B70" s="36" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B71" s="36" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B72" s="36" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B73" s="36" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="B74" s="36" t="s">
         <v>869</v>
-      </c>
-      <c r="B74" s="36" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B75" s="36" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B76" s="36" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B77" s="36" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="B78" s="36" t="s">
         <v>874</v>
-      </c>
-      <c r="B78" s="36" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B79" s="36" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B80" s="36" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B81" s="36" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B82" s="36" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B83" s="36" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B84" s="36" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B85" s="36" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B86" s="36" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B87" s="36" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B88" s="36" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B89" s="36" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B90" s="36" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B91" s="36" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B92" s="36" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B93" s="36" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B94" s="36" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
+        <v>891</v>
+      </c>
+      <c r="B95" s="36" t="s">
         <v>892</v>
-      </c>
-      <c r="B95" s="36" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="36" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="97" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B97" s="36" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="98" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B98" s="36" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="99" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B99" s="36" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="100" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B100" s="36" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="101" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B101" s="36" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="102" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B102" s="36" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="103" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B103" s="36" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="104" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B104" s="36" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="105" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B105" s="36" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="106" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B106" s="37" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="107" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B107" s="37" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="108" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B108" s="37" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="109" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B109" s="37" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="110" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B110" s="37" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="111" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B111" s="37" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="112" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B112" s="36" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="113" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B113" s="36" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="114" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B114" s="36" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="115" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B115" s="36" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="116" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B116" s="36" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="117" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B117" s="36" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="118" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B118" s="36" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="119" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B119" s="36" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="120" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B120" s="36" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="121" spans="2:2" ht="14.4" x14ac:dyDescent="0.3"/>
